--- a/Result/profitability/3624.xlsx
+++ b/Result/profitability/3624.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6025</v>
+        <v>0.6875</v>
       </c>
       <c r="N2" t="n">
-        <v>28.015</v>
+        <v>28.94625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>0.64</v>
+        <v>0.72875</v>
       </c>
       <c r="N3" t="n">
-        <v>30.1975</v>
+        <v>31.43375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0.62125</v>
+        <v>0.6925</v>
       </c>
       <c r="N4" t="n">
-        <v>30.82</v>
+        <v>31.59875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5525</v>
+        <v>0.6925</v>
       </c>
       <c r="N5" t="n">
-        <v>30.26625</v>
+        <v>30.73</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.59</v>
+        <v>0.64375</v>
       </c>
       <c r="N6" t="n">
-        <v>30.49375</v>
+        <v>31.81875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0.50625</v>
+        <v>0.56375</v>
       </c>
       <c r="N7" t="n">
-        <v>29.995</v>
+        <v>31.18125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.51125</v>
+        <v>0.5562499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>31.90375</v>
+        <v>32.4325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>1.09</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4924999999999999</v>
+        <v>0.4925</v>
       </c>
       <c r="N10" t="n">
         <v>32.77375</v>
@@ -9576,6 +9576,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3624</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>895</v>
+      </c>
+      <c r="D73" t="n">
+        <v>601</v>
+      </c>
+      <c r="E73" t="n">
+        <v>293</v>
+      </c>
+      <c r="F73" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="G73" t="n">
+        <v>166</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>18.51%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>9</v>
+      </c>
+      <c r="J73" t="n">
+        <v>174</v>
+      </c>
+      <c r="K73" t="n">
+        <v>131</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.5687500000000001</v>
+      </c>
+      <c r="N73" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.3600000000000001</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.4800000000000002</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.1481092436974789</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-112</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>3.710000000000001</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.1275790921595599</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
